--- a/Mediciones/RNA/L/RUN3_L_2NO.xlsx
+++ b/Mediciones/RNA/L/RUN3_L_2NO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GiHub\Resultados_Doc\Mediciones\RNA\L\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DBBCCF9-0198-4830-B1F0-29DA2F9A94B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592475BF-6C52-4466-8D35-61547B7B13BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -462,6 +462,9 @@
     <t>sensors_n_now</t>
   </si>
   <si>
+    <t>RNA</t>
+  </si>
+  <si>
     <t>{
   "timestamp": "2026-07-18T22:05:15",
   "bounds": {
@@ -472,7 +475,7 @@
   },
   "serial": {
     "port": "COM7",
-    "baud": "460800",
+    "baud": "115200",
     "eol": "LF",
     "send_enabled": true
   },
@@ -563,9 +566,6 @@
   "run_id": "R20260718_220515",
   "repetition": 1
 }</t>
-  </si>
-  <si>
-    <t>RNA</t>
   </si>
 </sst>
 </file>
@@ -921,7 +921,7 @@
     </row>
     <row r="2" spans="1:1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D2">
         <v>1.674082124085834E-2</v>
@@ -1080,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D3">
         <v>1.674082124085834E-2</v>
@@ -1134,7 +1134,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D4">
         <v>1.674082124085834E-2</v>
@@ -1188,7 +1188,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D5">
         <v>1.674082124085834E-2</v>
@@ -1242,7 +1242,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D6">
         <v>1.674082124085834E-2</v>
@@ -1296,7 +1296,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D7">
         <v>1.674082124085834E-2</v>
@@ -1350,7 +1350,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D8">
         <v>1.674082124085834E-2</v>
@@ -1404,7 +1404,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D9">
         <v>1.674082124085834E-2</v>
@@ -1458,7 +1458,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D10">
         <v>1.674082124085834E-2</v>
@@ -1512,7 +1512,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D11">
         <v>1.674082124085834E-2</v>
@@ -1566,7 +1566,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D12">
         <v>1.674082124085834E-2</v>
@@ -1620,7 +1620,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D13">
         <v>1.674082124085834E-2</v>
@@ -1674,7 +1674,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D14">
         <v>1.674082124085834E-2</v>
@@ -1728,7 +1728,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D15">
         <v>1.6999635601837738E-2</v>
@@ -1782,7 +1782,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D16">
         <v>1.6999635601837738E-2</v>
@@ -1836,7 +1836,7 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D17">
         <v>1.8350497054390999E-2</v>
@@ -1890,7 +1890,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D18">
         <v>1.8350497054390999E-2</v>
@@ -1944,7 +1944,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D19">
         <v>1.8350497054390999E-2</v>
@@ -1998,7 +1998,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D20">
         <v>1.8350497054390999E-2</v>
@@ -2052,7 +2052,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D21">
         <v>1.8350497054390999E-2</v>
@@ -2106,7 +2106,7 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D22">
         <v>1.8350497054390999E-2</v>
@@ -2160,7 +2160,7 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D23">
         <v>1.8350497054390999E-2</v>
@@ -2214,7 +2214,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D24">
         <v>1.8350497054390999E-2</v>
@@ -2268,7 +2268,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D25">
         <v>1.8350497054390999E-2</v>
@@ -2322,7 +2322,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D26">
         <v>1.8350497054390999E-2</v>
@@ -2376,7 +2376,7 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D27">
         <v>1.8350497054390999E-2</v>
@@ -2430,7 +2430,7 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D28">
         <v>1.8350497054390999E-2</v>
@@ -2484,7 +2484,7 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D29">
         <v>1.8350497054390999E-2</v>
@@ -2538,7 +2538,7 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D30">
         <v>1.8350497054390999E-2</v>
@@ -2592,7 +2592,7 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D31">
         <v>1.8350497054390999E-2</v>
@@ -2646,7 +2646,7 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D32">
         <v>1.8350497054390999E-2</v>
@@ -2700,7 +2700,7 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D33">
         <v>1.8350497054390999E-2</v>
@@ -2754,7 +2754,7 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D34">
         <v>1.8350497054390999E-2</v>
@@ -2808,7 +2808,7 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D35">
         <v>1.8350497054390999E-2</v>
@@ -2862,7 +2862,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D36">
         <v>1.8350497054390999E-2</v>
@@ -2916,7 +2916,7 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D37">
         <v>1.8350497054390999E-2</v>
@@ -2970,7 +2970,7 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D38">
         <v>1.8350497054390999E-2</v>
@@ -3024,7 +3024,7 @@
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D39">
         <v>1.8350497054390999E-2</v>
@@ -3078,7 +3078,7 @@
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D40">
         <v>1.925802967213458E-2</v>
@@ -3132,7 +3132,7 @@
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D41">
         <v>1.925802967213458E-2</v>
@@ -3186,7 +3186,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D42">
         <v>1.947205067260847E-2</v>
@@ -3240,7 +3240,7 @@
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D43">
         <v>2.595885554261769E-2</v>
@@ -3294,7 +3294,7 @@
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D44">
         <v>6.2481204796417167E-2</v>
@@ -3348,7 +3348,7 @@
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D45">
         <v>0.63814591946718369</v>
@@ -3402,7 +3402,7 @@
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D46">
         <v>0.80835209694523524</v>
@@ -3456,7 +3456,7 @@
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D47">
         <v>0.93794344963602283</v>
@@ -3510,7 +3510,7 @@
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D48">
         <v>0.99644257680669557</v>
@@ -3564,7 +3564,7 @@
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D49">
         <v>0.99644257680669557</v>
@@ -3618,7 +3618,7 @@
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D50">
         <v>0.99644257680669557</v>
@@ -3672,7 +3672,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D51">
         <v>0.99644257680669557</v>
@@ -3726,7 +3726,7 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D52">
         <v>0.99644257680669557</v>
@@ -3780,7 +3780,7 @@
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D53">
         <v>0.99644257680669557</v>
@@ -3834,7 +3834,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D54">
         <v>0.99644257680669557</v>
@@ -3888,7 +3888,7 @@
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D55">
         <v>0.99644257680669557</v>
@@ -3942,7 +3942,7 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D56">
         <v>0.99644257680669557</v>
@@ -3996,7 +3996,7 @@
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D57">
         <v>0.99644257680669557</v>
@@ -4050,7 +4050,7 @@
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D58">
         <v>0.99644257680669557</v>
@@ -4104,7 +4104,7 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D59">
         <v>0.99644257680669557</v>
@@ -4158,7 +4158,7 @@
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D60">
         <v>0.99644257680669557</v>
@@ -4212,7 +4212,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D61">
         <v>0.99644257680669557</v>
@@ -4266,7 +4266,7 @@
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D62">
         <v>0.99644257680669557</v>
@@ -4320,7 +4320,7 @@
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D63">
         <v>0.99644257680669557</v>
@@ -4374,7 +4374,7 @@
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D64">
         <v>0.99644257680669557</v>
@@ -4428,7 +4428,7 @@
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D65">
         <v>0.99644257680669557</v>
@@ -4482,7 +4482,7 @@
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D66">
         <v>0.99644257680669557</v>
@@ -4536,7 +4536,7 @@
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D67">
         <v>0.99644257680669557</v>
@@ -4590,7 +4590,7 @@
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D68">
         <v>0.99644257680669557</v>
@@ -4644,7 +4644,7 @@
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D69">
         <v>0.99644257680669557</v>
@@ -4698,7 +4698,7 @@
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D70">
         <v>0.99644257680669557</v>
@@ -4752,7 +4752,7 @@
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D71">
         <v>0.99644257680669557</v>
@@ -4806,7 +4806,7 @@
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D72">
         <v>0.99644257680669557</v>
@@ -4860,7 +4860,7 @@
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D73">
         <v>0.99644257680669557</v>
@@ -4914,7 +4914,7 @@
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D74">
         <v>0.99644257680669557</v>
@@ -4968,7 +4968,7 @@
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D75">
         <v>0.99644257680669557</v>
@@ -5022,7 +5022,7 @@
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D76">
         <v>0.99644257680669557</v>
@@ -5076,7 +5076,7 @@
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D77">
         <v>0.99644257680669557</v>
@@ -5130,7 +5130,7 @@
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D78">
         <v>0.99644257680669557</v>
@@ -5184,7 +5184,7 @@
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D79">
         <v>0.99644257680669557</v>
@@ -5238,7 +5238,7 @@
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D80">
         <v>0.99644257680669557</v>
@@ -5292,7 +5292,7 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D81">
         <v>0.99644257680669557</v>
@@ -5346,7 +5346,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D82">
         <v>0.99644257680669557</v>
@@ -5400,7 +5400,7 @@
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D83">
         <v>0.99644257680669557</v>
@@ -5454,7 +5454,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D84">
         <v>0.99644257680669557</v>
@@ -5508,7 +5508,7 @@
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D85">
         <v>0.99644257680669557</v>
@@ -5562,7 +5562,7 @@
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D86">
         <v>0.99644257680669557</v>
@@ -5616,7 +5616,7 @@
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D87">
         <v>0.99644257680669557</v>
@@ -5670,7 +5670,7 @@
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D88">
         <v>0.99644257680669557</v>
@@ -5724,7 +5724,7 @@
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D89">
         <v>0.99644257680669557</v>
@@ -5778,7 +5778,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D90">
         <v>0.99644257680669557</v>
@@ -5832,7 +5832,7 @@
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D91">
         <v>0.99644257680669557</v>
@@ -5886,7 +5886,7 @@
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D92">
         <v>0.99644257680669557</v>
@@ -5940,7 +5940,7 @@
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D93">
         <v>0.99644257680669557</v>
@@ -5994,7 +5994,7 @@
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D94">
         <v>0.99644257680669557</v>
@@ -6048,7 +6048,7 @@
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D95">
         <v>0.99644257680669557</v>
@@ -6102,7 +6102,7 @@
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D96">
         <v>0.99644257680669557</v>
@@ -6156,7 +6156,7 @@
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D97">
         <v>0.99644257680669557</v>
@@ -6210,7 +6210,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D98">
         <v>0.99644257680669557</v>
@@ -6264,7 +6264,7 @@
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D99">
         <v>0.99644257680669557</v>
@@ -6318,7 +6318,7 @@
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D100">
         <v>0.99644257680669557</v>
@@ -6372,7 +6372,7 @@
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D101">
         <v>0.99644257680669557</v>
@@ -6426,7 +6426,7 @@
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D102">
         <v>0.99644257680669557</v>
@@ -6480,7 +6480,7 @@
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D103">
         <v>0.99644257680669557</v>
@@ -6534,7 +6534,7 @@
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D104">
         <v>0.99644257680669557</v>
@@ -6588,7 +6588,7 @@
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D105">
         <v>0.99644257680669557</v>
@@ -6642,7 +6642,7 @@
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D106">
         <v>0.99644257680669557</v>
@@ -6696,7 +6696,7 @@
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D107">
         <v>0.99644257680669557</v>
@@ -6750,7 +6750,7 @@
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D108">
         <v>0.99644257680669557</v>
@@ -6804,7 +6804,7 @@
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D109">
         <v>0.99644257680669557</v>
@@ -6858,7 +6858,7 @@
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D110">
         <v>0.99644257680669557</v>
@@ -6912,7 +6912,7 @@
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D111">
         <v>0.99644257680669557</v>
@@ -6966,7 +6966,7 @@
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D112">
         <v>0.99644257680669557</v>
@@ -7020,7 +7020,7 @@
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D113">
         <v>0.99644257680669557</v>
@@ -7074,7 +7074,7 @@
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D114">
         <v>0.99644257680669557</v>
@@ -7128,7 +7128,7 @@
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D115">
         <v>0.99644257680669557</v>
@@ -7182,7 +7182,7 @@
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D116">
         <v>0.99644257680669557</v>
@@ -7236,7 +7236,7 @@
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D117">
         <v>0.99644257680669557</v>
@@ -7290,7 +7290,7 @@
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D118">
         <v>0.99644257680669557</v>
@@ -7344,7 +7344,7 @@
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D119">
         <v>0.99644257680669557</v>
@@ -7398,7 +7398,7 @@
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D120">
         <v>0.99644257680669557</v>
@@ -7452,7 +7452,7 @@
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D121">
         <v>0.99644257680669557</v>
@@ -12964,7 +12964,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
